--- a/diagramas/diagramaGantt.xlsx
+++ b/diagramas/diagramaGantt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universidaddeburgos-my.sharepoint.com/personal/mmm1059_alu_ubu_es/Documents/Escritorio/TFG-Marina-Martin/diagramas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{4FCC31AE-55C1-4CE4-B909-C81D660EA50D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7F5CB1F-8875-44B3-848E-196567BE897F}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="8_{4FCC31AE-55C1-4CE4-B909-C81D660EA50D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90289FE6-AA92-4D30-B006-FE78373B6E24}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{28BE8028-781D-4881-B67A-D6488C875A24}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="13">
   <si>
     <t>1. Revisión bibliográfica inicial</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>FIN PROYECTO</t>
+  </si>
+  <si>
+    <t>7. Redacción de los anexos</t>
   </si>
 </sst>
 </file>
@@ -249,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -257,19 +260,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -321,6 +311,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -355,6 +348,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -429,10 +434,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -752,7 +753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{711885E2-1D45-46E7-BDDE-F8AF0CEBD29E}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.77734375" customWidth="1"/>
@@ -760,171 +761,223 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="39">
+      <c r="C2" s="22"/>
+      <c r="D2" s="27">
         <v>45566</v>
       </c>
-      <c r="E2" s="40"/>
+      <c r="E2" s="28"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="41">
+      <c r="C3" s="26"/>
+      <c r="D3" s="29">
         <v>45816</v>
       </c>
-      <c r="E3" s="42"/>
+      <c r="E3" s="30"/>
     </row>
     <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="43">
+      <c r="C4" s="24"/>
+      <c r="D4" s="31">
         <f>D3-D2</f>
         <v>250</v>
       </c>
-      <c r="E4" s="44"/>
+      <c r="E4" s="32"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="8">
         <f>D2</f>
         <v>45566</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="8">
         <f>D6+31</f>
         <v>45597</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="8">
         <f>E6+30</f>
         <v>45627</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="8">
         <f>F6+31</f>
         <v>45658</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="8">
         <f>G6+31</f>
         <v>45689</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="8">
         <f>H6+28</f>
         <v>45717</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="8">
         <f>I6+31</f>
         <v>45748</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="8">
         <f>J6+30</f>
         <v>45778</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="9">
         <f>K6+31</f>
         <v>45809</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="33">
         <v>45566</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="33">
         <v>45613</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="9"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="5"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="33">
         <v>45597</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="33">
         <v>45703</v>
       </c>
-      <c r="L8" s="11"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="5"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="33">
         <v>45667</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="33">
         <v>45762</v>
       </c>
-      <c r="L9" s="11"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="5"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="33">
         <v>45731</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="33">
         <v>45767</v>
       </c>
-      <c r="L10" s="11"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="34"/>
+      <c r="K10" s="34"/>
+      <c r="L10" s="5"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="33">
         <v>45768</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="33">
         <v>45807</v>
       </c>
-      <c r="L11" s="11"/>
-    </row>
-    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="12" t="s">
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="34"/>
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="35">
         <v>45748</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="35">
         <v>45816</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="15"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="5"/>
+    </row>
+    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7">
+        <v>45782</v>
+      </c>
+      <c r="C13" s="7">
+        <v>45816</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -935,7 +988,7 @@
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="D4:E4"/>
   </mergeCells>
-  <conditionalFormatting sqref="D7:L12">
+  <conditionalFormatting sqref="D7:L12 K13:L13">
     <cfRule type="expression" priority="1">
       <formula>AND(D$6&gt;=$B7,D$6&lt;=$C7)</formula>
     </cfRule>
@@ -971,53 +1024,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="21">
+      <c r="D1" s="8">
         <v>45931</v>
       </c>
-      <c r="E1" s="21">
+      <c r="E1" s="8">
         <f>D1+31</f>
         <v>45962</v>
       </c>
-      <c r="F1" s="21">
+      <c r="F1" s="8">
         <f>E1+30</f>
         <v>45992</v>
       </c>
-      <c r="G1" s="21">
+      <c r="G1" s="8">
         <f>F1+31</f>
         <v>46023</v>
       </c>
-      <c r="H1" s="21">
+      <c r="H1" s="8">
         <f>G1+31</f>
         <v>46054</v>
       </c>
-      <c r="I1" s="21">
+      <c r="I1" s="8">
         <f>H1+28</f>
         <v>46082</v>
       </c>
-      <c r="J1" s="21">
+      <c r="J1" s="8">
         <f>I1+31</f>
         <v>46113</v>
       </c>
-      <c r="K1" s="21">
+      <c r="K1" s="8">
         <f>J1+30</f>
         <v>46143</v>
       </c>
-      <c r="L1" s="22">
+      <c r="L1" s="9">
         <f>K1+31</f>
         <v>46174</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2">
@@ -1026,18 +1079,18 @@
       <c r="C2" s="2">
         <v>45613</v>
       </c>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="26"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="13"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="1">
@@ -1046,18 +1099,18 @@
       <c r="C3" s="1">
         <v>45703</v>
       </c>
-      <c r="D3" s="28"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="18"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="5"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="14" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1">
@@ -1066,18 +1119,18 @@
       <c r="C4" s="1">
         <v>45769</v>
       </c>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="18"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="5"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="14" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="1">
@@ -1086,18 +1139,18 @@
       <c r="C5" s="1">
         <v>45777</v>
       </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="18"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="5"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="14" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="1">
@@ -1106,35 +1159,35 @@
       <c r="C6" s="1">
         <v>45807</v>
       </c>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="18"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="5"/>
     </row>
     <row r="7" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="7">
         <v>45748</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="7">
         <v>45816</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="32"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="19"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:L7">
